--- a/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10395" windowHeight="9735" activeTab="2"/>
+    <workbookView windowWidth="11190" windowHeight="9990" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>名称</t>
   </si>
@@ -44,12 +44,12 @@
     <t>圣殿弩手</t>
   </si>
   <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
     <t>增援战线</t>
   </si>
   <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
     <t>光明惩戒</t>
   </si>
   <si>
@@ -59,12 +59,12 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
     <t>传记·钢铁守卫</t>
   </si>
   <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
     <t>圣殿御卫</t>
   </si>
   <si>
@@ -77,9 +77,6 @@
     <t>召集护卫</t>
   </si>
   <si>
-    <t>夺取阵地</t>
-  </si>
-  <si>
     <t>炽阳坠落</t>
   </si>
   <si>
@@ -119,21 +116,18 @@
     <t>心灵黑洞2</t>
   </si>
   <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
     <t>黑夜突袭</t>
   </si>
   <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
     <t>酗酒醉汉</t>
   </si>
   <si>
     <t>不法交易</t>
   </si>
   <si>
-    <t>黑旗舰队飞斧手</t>
-  </si>
-  <si>
     <t>海燕精卫</t>
   </si>
   <si>
@@ -146,58 +140,61 @@
     <t>黑金诈术师</t>
   </si>
   <si>
-    <t>烈日大祭师</t>
-  </si>
-  <si>
     <t>黑旗舰队船长</t>
   </si>
   <si>
     <t>海燕·鲍莉</t>
   </si>
   <si>
+    <t>欢乐歌唱的戴维</t>
+  </si>
+  <si>
     <t>戴维的惊天计谋</t>
   </si>
   <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
     <t>港口卡等：</t>
   </si>
   <si>
     <t>愚笨鲸头鹅</t>
   </si>
   <si>
+    <t>旷野祭师</t>
+  </si>
+  <si>
+    <t>蓄力射手</t>
+  </si>
+  <si>
     <t>势如破竹</t>
   </si>
   <si>
-    <t>蓄力射手</t>
-  </si>
-  <si>
-    <t>迅捷长矛手</t>
-  </si>
-  <si>
     <t>强行捕猎</t>
   </si>
   <si>
     <t>无畏猎户</t>
   </si>
   <si>
+    <t>诱敌草人</t>
+  </si>
+  <si>
     <t>肥鼠晚宴</t>
   </si>
   <si>
+    <t>活力仙人掌</t>
+  </si>
+  <si>
     <t>地洞巨獾</t>
   </si>
   <si>
-    <t>活力仙人掌</t>
-  </si>
-  <si>
-    <t>圣兽祭师</t>
-  </si>
-  <si>
     <t>飞斧狂人</t>
   </si>
   <si>
     <t>饥蛮巨汉</t>
   </si>
   <si>
-    <t>飞斧女豪</t>
+    <t>贪食白龙</t>
   </si>
   <si>
     <t>血饮烈斧·凯</t>
@@ -1167,7 +1164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1175,7 +1172,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1186,7 +1183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1197,7 +1194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1208,7 +1205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1216,10 +1213,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,12 +1227,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1249,11 +1246,11 @@
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>21.25</v>
+        <v>21.5</v>
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1264,7 +1261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1272,10 +1269,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1283,10 +1280,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1297,7 +1294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
@@ -1308,7 +1305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1316,7 +1313,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1331,15 +1328,9 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>16</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1347,20 +1338,26 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>20.5714285714286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C11:C18)</f>
-        <v>19.5</v>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1368,10 +1365,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1382,7 +1379,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1390,10 +1387,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1401,10 +1398,10 @@
         <v>21</v>
       </c>
       <c r="B27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1412,22 +1409,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="3">
-        <v>8</v>
-      </c>
-      <c r="C29" s="3">
-        <v>19</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3"/>
@@ -1435,39 +1426,34 @@
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
+      <c r="A31" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C23:C28)</f>
+        <v>20.8333333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="3">
-        <f>AVERAGE(C24:C29)</f>
-        <v>19.8333333333333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="4">
-        <f>AVERAGE(C2:C5,C11:C18,C24:C29)</f>
-        <v>20</v>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
+        <v>20.8823529411765</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C35 C8" formulaRange="1"/>
+    <ignoredError sqref="C8 C34" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1483,7 +1469,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1494,31 +1480,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1527,181 +1513,181 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>19.8571428571429</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>20.5</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C13:C17)</f>
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="2">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C14:C19)</f>
-        <v>19.5</v>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3">
         <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1719,23 +1705,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>16.5</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C19,C25:C26)</f>
-        <v>19.2666666666667</v>
+        <f>AVERAGE(C2:C7,C13:C17,C23:C26)</f>
+        <v>19.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1755,7 +1741,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1766,20 +1752,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1788,56 +1774,56 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1851,96 +1837,96 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>18</v>
+        <v>19.6666666666667</v>
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1958,22 +1944,22 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C13:C20)</f>
-        <v>17</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1991,23 +1977,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>17.2</v>
+        <v>18.9333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\akuiCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11190" windowHeight="9990" activeTab="2"/>
+    <workbookView windowWidth="13665" windowHeight="9975" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -41,10 +46,10 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
+    <t>炫目神光</t>
+  </si>
+  <si>
+    <t>塔楼弓手</t>
   </si>
   <si>
     <t>增援战线</t>
@@ -59,13 +64,13 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
     <t>四芒军旗</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
+    <t>热血冒险家</t>
   </si>
   <si>
     <t>白袍主教</t>
@@ -137,12 +142,12 @@
     <t>黑水伏击</t>
   </si>
   <si>
+    <t>寒夜灯灵</t>
+  </si>
+  <si>
     <t>黑金诈术师</t>
   </si>
   <si>
-    <t>黑旗舰队船长</t>
-  </si>
-  <si>
     <t>海燕·鲍莉</t>
   </si>
   <si>
@@ -164,9 +169,6 @@
     <t>旷野祭师</t>
   </si>
   <si>
-    <t>蓄力射手</t>
-  </si>
-  <si>
     <t>势如破竹</t>
   </si>
   <si>
@@ -185,19 +187,22 @@
     <t>活力仙人掌</t>
   </si>
   <si>
-    <t>地洞巨獾</t>
-  </si>
-  <si>
     <t>飞斧狂人</t>
   </si>
   <si>
     <t>饥蛮巨汉</t>
   </si>
   <si>
+    <t>石斧头领</t>
+  </si>
+  <si>
     <t>贪食白龙</t>
   </si>
   <si>
     <t>血饮烈斧·凯</t>
+  </si>
+  <si>
+    <t>原野大祭师·鲁玛</t>
   </si>
   <si>
     <t>蛮石卡等：</t>
@@ -1188,10 +1193,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1202,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1213,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1224,7 +1229,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1246,7 +1251,7 @@
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -1258,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1280,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1291,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1302,7 +1307,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1324,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1346,7 +1351,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>20.5714285714286</v>
+        <v>21.1428571428571</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1357,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1368,7 +1373,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1379,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1390,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1401,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1412,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1434,7 +1439,7 @@
       </c>
       <c r="C31" s="3">
         <f>AVERAGE(C23:C28)</f>
-        <v>20.8333333333333</v>
+        <v>21.8333333333333</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1446,14 +1451,14 @@
       </c>
       <c r="C34" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
-        <v>20.8823529411765</v>
+        <v>21.5882352941176</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C8 C34" formulaRange="1"/>
+    <ignoredError sqref="C34 C8" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1488,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1543,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1565,7 +1570,7 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>20.5</v>
+        <v>20.8333333333333</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -1577,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1588,7 +1593,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1607,10 +1612,10 @@
         <v>35</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1618,10 +1623,10 @@
         <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1643,7 +1648,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C13:C17)</f>
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1654,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1665,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1676,7 +1681,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1687,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1709,7 +1714,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1721,7 +1726,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C7,C13:C17,C23:C26)</f>
-        <v>19.5333333333333</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1771,7 +1776,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1790,15 +1795,15 @@
         <v>45</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
@@ -1808,15 +1813,9 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>17</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
@@ -1824,22 +1823,28 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>19.6666666666667</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>19</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
@@ -1849,7 +1854,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1857,10 +1862,10 @@
         <v>48</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1871,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1879,10 +1884,10 @@
         <v>50</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1890,10 +1895,10 @@
         <v>51</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1901,7 +1906,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2">
         <v>20</v>
@@ -1912,22 +1917,16 @@
         <v>53</v>
       </c>
       <c r="B19" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="2">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2">
-        <v>17</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -1935,20 +1934,26 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C13:C20)</f>
-        <v>18.75</v>
+      <c r="C22" s="2">
+        <f>AVERAGE(C12:C19)</f>
+        <v>19.625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1956,10 +1961,10 @@
         <v>55</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1980,8 +1985,8 @@
         <v>23</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C26:C26)</f>
-        <v>16</v>
+        <f>AVERAGE(C25:C26)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1992,8 +1997,8 @@
         <v>56</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>18.9333333333333</v>
+        <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>
